--- a/audit/qa-integral-dataset/fixtures/QA_cutover_hatchery.xlsx
+++ b/audit/qa-integral-dataset/fixtures/QA_cutover_hatchery.xlsx
@@ -1554,7 +1554,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-18T01:14:59.141325+00:00</t>
+          <t>2026-10-18T03:03:40.458456+00:00</t>
         </is>
       </c>
     </row>

--- a/audit/qa-integral-dataset/fixtures/QA_cutover_hatchery.xlsx
+++ b/audit/qa-integral-dataset/fixtures/QA_cutover_hatchery.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -890,12 +890,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>reception_date</t>
+          <t>egg_origin</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fecha de recepción del huevo en la planta. ≤ corte.</t>
+          <t>Origen comercial del huevo: internal (propio de Global Avícola) o purchased (comprado a un tercero). No es la generación biológica.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -905,17 +905,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>enum</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AAAA-MM-DD</t>
+          <t>uno de la lista</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>internal</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>internal, purchased</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -930,24 +935,24 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>lots.start_date, hatchery_openings.reception_date, opening_balances.activation_date</t>
+          <t>hatchery_openings.egg_origin</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>set_date</t>
+          <t>reception_date</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fecha de carga en incubadora. Vacío = desconocida; N/A = aún no cargado.</t>
+          <t>Fecha de recepción del huevo en la planta. ≤ corte.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -962,34 +967,34 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no (obligatorio)</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>hatchery_openings.set_date</t>
+          <t>lots.start_date, hatchery_openings.reception_date, opening_balances.activation_date</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>expected_hatch_date</t>
+          <t>set_date</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fecha prevista de nacimiento. ≥ fecha de carga.</t>
+          <t>Fecha de carga en incubadora. Vacío = desconocida; N/A = aún no cargado.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1009,7 +1014,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1024,71 +1029,66 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>hatchery_openings.expected_hatch_date</t>
+          <t>hatchery_openings.set_date</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>eggs_received</t>
+          <t>expected_hatch_date</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Huevos fértiles recibidos en la planta.</t>
+          <t>Fecha prevista de nacimiento. ≥ fecha de carga.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>AAAA-MM-DD</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>huevos</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>entero ≥ 0</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>10000</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>no (obligatorio)</t>
-        </is>
-      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>hatchery_openings.eggs_received</t>
+          <t>hatchery_openings.expected_hatch_date</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>eggs_set</t>
+          <t>eggs_received</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Huevos ya cargados en incubadora. ≤ recibidos.</t>
+          <t>Huevos fértiles recibidos en la planta.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1128,24 +1128,24 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>hatchery_openings.eggs_set</t>
+          <t>hatchery_openings.eggs_received</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>eggs_transferred</t>
+          <t>eggs_set</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Huevos ya transferidos a nacedora. ≤ cargados.</t>
+          <t>Huevos ya cargados en incubadora. ≤ recibidos.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1165,34 +1165,34 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no (obligatorio)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>hatchery_openings.eggs_transferred</t>
+          <t>hatchery_openings.eggs_set</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>eggs_discarded</t>
+          <t>eggs_transferred</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Huevos descartados (ovoscopia, rotos) del proceso. ≤ cargados.</t>
+          <t>Huevos ya transferidos a nacedora. ≤ cargados.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1232,19 +1232,19 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>hatchery_openings.eggs_discarded</t>
+          <t>hatchery_openings.eggs_transferred</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>chicks_hatched</t>
+          <t>eggs_discarded</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pollitos ya nacidos del proceso antes del corte.</t>
+          <t>Huevos descartados (ovoscopia, rotos) del proceso. ≤ cargados.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>pollitos</t>
+          <t>huevos</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1284,19 +1284,19 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>opening_balances.accumulated_chicks_hatched</t>
+          <t>hatchery_openings.eggs_discarded</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>chicks_available</t>
+          <t>chicks_hatched</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pollitos nacidos que siguen en planta sin despachar al corte.</t>
+          <t>Pollitos ya nacidos del proceso antes del corte.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1336,19 +1336,19 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>opening_balances.initial_mixed_count</t>
+          <t>opening_balances.accumulated_chicks_hatched</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>source_system</t>
+          <t>chicks_available</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sistema de origen del dato (p. ej. LEGACY, SAP, EXCEL). Vacío = el del batch.</t>
+          <t>Pollitos nacidos que siguen en planta sin despachar al corte.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1358,44 +1358,49 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>pollitos</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>entero ≥ 0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>LEGACY</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>vacío = sin dato</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>lots.source_system, opening_balances.source_system</t>
+          <t>opening_balances.initial_mixed_count</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>source_reference</t>
+          <t>source_system</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Referencia en el sistema de origen (documento, planilla, lote).</t>
+          <t>Sistema de origen del dato (p. ej. LEGACY, SAP, EXCEL). Vacío = el del batch.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1415,7 +1420,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>PLANILLA-2026-10</t>
+          <t>LEGACY</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1430,47 +1435,94 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>lots.source_reference, opening_balances.source_reference</t>
+          <t>lots.source_system, opening_balances.source_system</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>source_reference</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Referencia en el sistema de origen (documento, planilla, lote).</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>PLANILLA-2026-10</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>vacío = sin dato</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>lots.source_reference, opening_balances.source_reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>Notas libres. Nunca sustituyen a un campo del contrato.</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>texto</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>vacío = sin dato</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>cutover_items.opening_state.notes</t>
         </is>
@@ -1510,7 +1562,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>v3</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1574,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CUTOVER_HATCHERY_V2</t>
+          <t>CUTOVER_HATCHERY_V3</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1606,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-18T03:03:40.458456+00:00</t>
+          <t>2026-10-23T10:13:29.948225+00:00</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1586,18 +1638,19 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="15" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1638,60 +1691,65 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>egg_origin</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>reception_date</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>set_date</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>expected_hatch_date</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>eggs_received</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>eggs_set</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>eggs_transferred</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>eggs_discarded</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>chicks_hatched</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>chicks_available</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>source_system</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>source_reference</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -1725,45 +1783,130 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>internal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
         <v>12000</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>11000</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>150</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>LEGACY</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>QA-FIXTURE-HAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QA-CUT-HAT-NEW-002</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>QA-INC-01</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>QA Incubadora A1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>QA Nacedora N1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>grandparent</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>purchased</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>9000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>8500</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>100</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>LEGACY</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>QA-FIXTURE-HAT-PURCHASED</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>huevo comprado (purchased): sin lote fuente interno</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1807,6 +1950,11 @@
           <t>parent_code</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
